--- a/KNK업무시스템구축_엑셀/V2/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V2/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
